--- a/12624861.xlsx
+++ b/12624861.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0d631a768087d331/Documents/CAP776/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0d631a768087d331/Desktop/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="821" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58B8A7F2-613C-44F7-B6B7-FAB7EFD3ACC4}"/>
+  <xr:revisionPtr revIDLastSave="826" documentId="8_{B77C434B-7271-4DC5-97B4-D8EF94629151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33A2147E-2689-4471-BA7F-1AC04601542D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -538,10 +538,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1088,11 +1084,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f>IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J58" si="0">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J58" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1134,11 +1130,11 @@
         <v>30</v>
       </c>
       <c r="I7" s="15">
-        <f>IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <f t="shared" si="0"/>
         <v>730</v>
       </c>
       <c r="J7" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>710</v>
       </c>
       <c r="K7" s="16" t="s">
@@ -1178,11 +1174,11 @@
         <v>100</v>
       </c>
       <c r="I8" s="15">
-        <f>IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
+        <f t="shared" si="0"/>
         <v>840</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>600</v>
       </c>
       <c r="K8" s="16" t="s">
@@ -1222,11 +1218,11 @@
         <v>90</v>
       </c>
       <c r="I9" s="15">
-        <f>IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
+        <f t="shared" si="0"/>
         <v>1080</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>360</v>
       </c>
       <c r="K9" s="16" t="s">
@@ -1266,11 +1262,11 @@
         <v>90</v>
       </c>
       <c r="I10" s="15">
-        <f>IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
+        <f t="shared" si="0"/>
         <v>1070</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>370</v>
       </c>
       <c r="K10" s="16" t="s">
@@ -1310,11 +1306,11 @@
         <v>90</v>
       </c>
       <c r="I11" s="15">
-        <f>IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
+        <f t="shared" si="0"/>
         <v>1040</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
       <c r="K11" s="16" t="s">
@@ -1354,11 +1350,11 @@
         <v>90</v>
       </c>
       <c r="I12" s="15">
-        <f>IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
+        <f t="shared" si="0"/>
         <v>1130</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="K12" s="16" t="s">
@@ -1398,11 +1394,11 @@
         <v>90</v>
       </c>
       <c r="I13" s="15">
-        <f>IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
+        <f t="shared" si="0"/>
         <v>1220</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>220</v>
       </c>
       <c r="K13" s="16" t="s">
@@ -1442,11 +1438,11 @@
         <v>90</v>
       </c>
       <c r="I14" s="15">
-        <f>IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
+        <f t="shared" si="0"/>
         <v>841</v>
       </c>
       <c r="J14" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>599</v>
       </c>
       <c r="K14" s="16" t="s">
@@ -1486,11 +1482,11 @@
         <v>90</v>
       </c>
       <c r="I15" s="15">
-        <f>IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
+        <f t="shared" si="0"/>
         <v>852</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>588</v>
       </c>
       <c r="K15" s="16" t="s">
@@ -1530,11 +1526,11 @@
         <v>90</v>
       </c>
       <c r="I16" s="15">
-        <f>IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
+        <f t="shared" si="0"/>
         <v>980</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>460</v>
       </c>
       <c r="K16" s="16" t="s">
@@ -1574,11 +1570,11 @@
         <v>90</v>
       </c>
       <c r="I17" s="15">
-        <f>IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
+        <f t="shared" si="0"/>
         <v>1040</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
       <c r="K17" s="16" t="s">
@@ -1618,11 +1614,11 @@
         <v>90</v>
       </c>
       <c r="I18" s="15">
-        <f>IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
+        <f t="shared" si="0"/>
         <v>930</v>
       </c>
       <c r="J18" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>510</v>
       </c>
       <c r="K18" s="16" t="s">
@@ -1662,11 +1658,11 @@
         <v>90</v>
       </c>
       <c r="I19" s="15">
-        <f>IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
+        <f t="shared" si="0"/>
         <v>1060</v>
       </c>
       <c r="J19" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>380</v>
       </c>
       <c r="K19" s="16" t="s">
@@ -1706,11 +1702,11 @@
         <v>80</v>
       </c>
       <c r="I20" s="15">
-        <f>IF(SUM(B20:F20,H20)=0,"",SUM(B20:F20,H20))</f>
+        <f t="shared" si="0"/>
         <v>1070</v>
       </c>
       <c r="J20" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>370</v>
       </c>
       <c r="K20" s="16" t="s">
@@ -1750,11 +1746,11 @@
         <v>90</v>
       </c>
       <c r="I21" s="15">
-        <f>IF(SUM(B21:F21,H21)=0,"",SUM(B21:F21,H21))</f>
+        <f t="shared" si="0"/>
         <v>710</v>
       </c>
       <c r="J21" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>730</v>
       </c>
       <c r="K21" s="16" t="s">
@@ -1794,11 +1790,11 @@
         <v>90</v>
       </c>
       <c r="I22" s="15">
-        <f>IF(SUM(B22:F22,H22)=0,"",SUM(B22:F22,H22))</f>
+        <f t="shared" si="0"/>
         <v>740</v>
       </c>
       <c r="J22" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>700</v>
       </c>
       <c r="K22" s="16" t="s">
@@ -1838,11 +1834,11 @@
         <v>90</v>
       </c>
       <c r="I23" s="15">
-        <f>IF(SUM(B23:F23,H23)=0,"",SUM(B23:F23,H23))</f>
+        <f t="shared" si="0"/>
         <v>970</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>470</v>
       </c>
       <c r="K23" s="14" t="s">
@@ -1882,11 +1878,11 @@
         <v>100</v>
       </c>
       <c r="I24" s="15">
-        <f>IF(SUM(B24:F24,H24)=0,"",SUM(B24:F24,H24))</f>
+        <f t="shared" si="0"/>
         <v>1072</v>
       </c>
       <c r="J24" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>368</v>
       </c>
       <c r="K24" s="14" t="s">
@@ -1926,11 +1922,11 @@
         <v>100</v>
       </c>
       <c r="I25" s="15">
-        <f>IF(SUM(B25:F25,H25)=0,"",SUM(B25:F25,H25))</f>
+        <f t="shared" si="0"/>
         <v>1050</v>
       </c>
       <c r="J25" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>390</v>
       </c>
       <c r="K25" s="16" t="s">
@@ -1970,11 +1966,11 @@
         <v>90</v>
       </c>
       <c r="I26" s="15">
-        <f>IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
+        <f t="shared" si="0"/>
         <v>1159</v>
       </c>
       <c r="J26" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>281</v>
       </c>
       <c r="K26" s="14" t="s">
@@ -2014,11 +2010,11 @@
         <v>95</v>
       </c>
       <c r="I27" s="15">
-        <f>IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
+        <f t="shared" si="0"/>
         <v>1135</v>
       </c>
       <c r="J27" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>305</v>
       </c>
       <c r="K27" s="14" t="s">
@@ -2058,11 +2054,11 @@
         <v>90</v>
       </c>
       <c r="I28" s="15">
-        <f>IF(SUM(B28:F28,H28)=0,"",SUM(B28:F28,H28))</f>
+        <f t="shared" si="0"/>
         <v>876</v>
       </c>
       <c r="J28" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>564</v>
       </c>
       <c r="K28" s="14" t="s">
@@ -2102,11 +2098,11 @@
         <v>95</v>
       </c>
       <c r="I29" s="15">
-        <f>IF(SUM(B29:F29,H29)=0,"",SUM(B29:F29,H29))</f>
+        <f t="shared" si="0"/>
         <v>755</v>
       </c>
       <c r="J29" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>685</v>
       </c>
       <c r="K29" s="14" t="s">
@@ -2146,11 +2142,11 @@
         <v>95</v>
       </c>
       <c r="I30" s="15">
-        <f>IF(SUM(B30:F30,H30)=0,"",SUM(B30:F30,H30))</f>
+        <f t="shared" si="0"/>
         <v>1045</v>
       </c>
       <c r="J30" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>395</v>
       </c>
       <c r="K30" s="14" t="s">
@@ -2190,11 +2186,11 @@
         <v>95</v>
       </c>
       <c r="I31" s="15">
-        <f>IF(SUM(B31:F31,H31)=0,"",SUM(B31:F31,H31))</f>
+        <f t="shared" si="0"/>
         <v>1155</v>
       </c>
       <c r="J31" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>285</v>
       </c>
       <c r="K31" s="14" t="s">
@@ -2234,11 +2230,11 @@
         <v>96</v>
       </c>
       <c r="I32" s="15">
-        <f>IF(SUM(B32:F32,H32)=0,"",SUM(B32:F32,H32))</f>
+        <f t="shared" si="0"/>
         <v>1012</v>
       </c>
       <c r="J32" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>428</v>
       </c>
       <c r="K32" s="14" t="s">
@@ -2278,11 +2274,11 @@
         <v>90</v>
       </c>
       <c r="I33" s="15">
-        <f>IF(SUM(B33:F33,H33)=0,"",SUM(B33:F33,H33))</f>
+        <f t="shared" si="0"/>
         <v>1130</v>
       </c>
       <c r="J33" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="K33" s="14" t="s">
@@ -2322,11 +2318,11 @@
         <v>80</v>
       </c>
       <c r="I34" s="15">
-        <f>IF(SUM(B34:F34,H34)=0,"",SUM(B34:F34,H34))</f>
+        <f t="shared" si="0"/>
         <v>1164</v>
       </c>
       <c r="J34" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>276</v>
       </c>
       <c r="K34" s="16" t="s">
@@ -2366,11 +2362,11 @@
         <v>80</v>
       </c>
       <c r="I35" s="15">
-        <f>IF(SUM(B35:F35,H35)=0,"",SUM(B35:F35,H35))</f>
+        <f t="shared" si="0"/>
         <v>825</v>
       </c>
       <c r="J35" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>615</v>
       </c>
       <c r="K35" s="16" t="s">
@@ -2410,11 +2406,11 @@
         <v>85</v>
       </c>
       <c r="I36" s="15">
-        <f>IF(SUM(B36:F36,H36)=0,"",SUM(B36:F36,H36))</f>
+        <f t="shared" si="0"/>
         <v>855</v>
       </c>
       <c r="J36" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>585</v>
       </c>
       <c r="K36" s="16" t="s">
@@ -2454,11 +2450,11 @@
         <v>89</v>
       </c>
       <c r="I37" s="15">
-        <f>IF(SUM(B37:F37,H37)=0,"",SUM(B37:F37,H37))</f>
+        <f t="shared" si="0"/>
         <v>1042</v>
       </c>
       <c r="J37" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>398</v>
       </c>
       <c r="K37" s="14" t="s">
@@ -2498,11 +2494,11 @@
         <v>90</v>
       </c>
       <c r="I38" s="15">
-        <f>IF(SUM(B38:F38,H38)=0,"",SUM(B38:F38,H38))</f>
+        <f t="shared" si="0"/>
         <v>1059</v>
       </c>
       <c r="J38" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>381</v>
       </c>
       <c r="K38" s="14" t="s">
@@ -2542,11 +2538,11 @@
         <v>90</v>
       </c>
       <c r="I39" s="15">
-        <f>IF(SUM(B39:F39,H39)=0,"",SUM(B39:F39,H39))</f>
+        <f t="shared" si="0"/>
         <v>1032</v>
       </c>
       <c r="J39" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>408</v>
       </c>
       <c r="K39" s="16" t="s">
@@ -2586,11 +2582,11 @@
         <v>120</v>
       </c>
       <c r="I40" s="15">
-        <f>IF(SUM(B40:F40,H40)=0,"",SUM(B40:F40,H40))</f>
+        <f t="shared" si="0"/>
         <v>1130</v>
       </c>
       <c r="J40" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="K40" s="14" t="s">
@@ -2630,11 +2626,11 @@
         <v>120</v>
       </c>
       <c r="I41" s="15">
-        <f>IF(SUM(B41:F41,H41)=0,"",SUM(B41:F41,H41))</f>
+        <f t="shared" si="0"/>
         <v>1195</v>
       </c>
       <c r="J41" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>245</v>
       </c>
       <c r="K41" s="14" t="s">
@@ -2674,11 +2670,11 @@
         <v>150</v>
       </c>
       <c r="I42" s="15">
-        <f>IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
+        <f t="shared" si="0"/>
         <v>906</v>
       </c>
       <c r="J42" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>534</v>
       </c>
       <c r="K42" s="14" t="s">
@@ -2718,11 +2714,11 @@
         <v>160</v>
       </c>
       <c r="I43" s="15">
-        <f>IF(SUM(B43:F43,H43)=0,"",SUM(B43:F43,H43))</f>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J43" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>550</v>
       </c>
       <c r="K43" s="14" t="s">
@@ -2762,11 +2758,11 @@
         <v>130</v>
       </c>
       <c r="I44" s="15">
-        <f>IF(SUM(B44:F44,H44)=0,"",SUM(B44:F44,H44))</f>
+        <f t="shared" si="0"/>
         <v>1130</v>
       </c>
       <c r="J44" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>310</v>
       </c>
       <c r="K44" s="14" t="s">
@@ -2806,11 +2802,11 @@
         <v>140</v>
       </c>
       <c r="I45" s="15">
-        <f>IF(SUM(B45:F45,H45)=0,"",SUM(B45:F45,H45))</f>
+        <f t="shared" si="0"/>
         <v>1100</v>
       </c>
       <c r="J45" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>340</v>
       </c>
       <c r="K45" s="14" t="s">
@@ -2850,11 +2846,11 @@
         <v>150</v>
       </c>
       <c r="I46" s="15">
-        <f>IF(SUM(B46:F46,H46)=0,"",SUM(B46:F46,H46))</f>
+        <f t="shared" si="0"/>
         <v>1090</v>
       </c>
       <c r="J46" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>350</v>
       </c>
       <c r="K46" s="14" t="s">
@@ -2894,11 +2890,11 @@
         <v>160</v>
       </c>
       <c r="I47" s="15">
-        <f>IF(SUM(B47:F47,H47)=0,"",SUM(B47:F47,H47))</f>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="J47" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>240</v>
       </c>
       <c r="K47" s="14" t="s">
@@ -2938,11 +2934,11 @@
         <v>130</v>
       </c>
       <c r="I48" s="15">
-        <f>IF(SUM(B48:F48,H48)=0,"",SUM(B48:F48,H48))</f>
+        <f t="shared" si="0"/>
         <v>1262</v>
       </c>
       <c r="J48" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>178</v>
       </c>
       <c r="K48" s="16" t="s">
@@ -2982,11 +2978,11 @@
         <v>120</v>
       </c>
       <c r="I49" s="15">
-        <f>IF(SUM(B49:F49,H49)=0,"",SUM(B49:F49,H49))</f>
+        <f t="shared" si="0"/>
         <v>896</v>
       </c>
       <c r="J49" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>544</v>
       </c>
       <c r="K49" s="16" t="s">
@@ -3026,11 +3022,11 @@
         <v>100</v>
       </c>
       <c r="I50" s="15">
-        <f>IF(SUM(B50:F50,H50)=0,"",SUM(B50:F50,H50))</f>
+        <f t="shared" si="0"/>
         <v>863</v>
       </c>
       <c r="J50" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>577</v>
       </c>
       <c r="K50" s="16" t="s">
@@ -3070,11 +3066,11 @@
         <v>120</v>
       </c>
       <c r="I51" s="15">
-        <f>IF(SUM(B51:F51,H51)=0,"",SUM(B51:F51,H51))</f>
+        <f t="shared" si="0"/>
         <v>1085</v>
       </c>
       <c r="J51" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>355</v>
       </c>
       <c r="K51" s="16" t="s">
@@ -3114,11 +3110,11 @@
         <v>130</v>
       </c>
       <c r="I52" s="15">
-        <f>IF(SUM(B52:F52,H52)=0,"",SUM(B52:F52,H52))</f>
+        <f t="shared" si="0"/>
         <v>1127</v>
       </c>
       <c r="J52" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>313</v>
       </c>
       <c r="K52" s="16" t="s">
@@ -3154,14 +3150,16 @@
       <c r="G53" s="14">
         <v>4</v>
       </c>
-      <c r="H53" s="14"/>
+      <c r="H53" s="14">
+        <v>565</v>
+      </c>
       <c r="I53" s="15">
-        <f>IF(SUM(B53:F53,H53)=0,"",SUM(B53:F53,H53))</f>
-        <v>875</v>
+        <f t="shared" si="0"/>
+        <v>1440</v>
       </c>
       <c r="J53" s="15">
-        <f t="shared" si="0"/>
-        <v>565</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="K53" s="16" t="s">
         <v>59</v>
@@ -3200,11 +3198,11 @@
         <v>100</v>
       </c>
       <c r="I54" s="15">
-        <f>IF(SUM(B54:F54,H54)=0,"",SUM(B54:F54,H54))</f>
+        <f t="shared" si="0"/>
         <v>1128</v>
       </c>
       <c r="J54" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>312</v>
       </c>
       <c r="K54" s="16" t="s">
@@ -3244,11 +3242,11 @@
         <v>100</v>
       </c>
       <c r="I55" s="15">
-        <f>IF(SUM(B55:F55,H55)=0,"",SUM(B55:F55,H55))</f>
+        <f t="shared" si="0"/>
         <v>1177</v>
       </c>
       <c r="J55" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>263</v>
       </c>
       <c r="K55" s="16" t="s">
@@ -3288,11 +3286,11 @@
         <v>100</v>
       </c>
       <c r="I56" s="15">
-        <f>IF(SUM(B56:F56,H56)=0,"",SUM(B56:F56,H56))</f>
+        <f t="shared" si="0"/>
         <v>846</v>
       </c>
       <c r="J56" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>594</v>
       </c>
       <c r="K56" s="16" t="s">
@@ -3332,11 +3330,11 @@
         <v>150</v>
       </c>
       <c r="I57" s="15">
-        <f>IF(SUM(B57:F57,H57)=0,"",SUM(B57:F57,H57))</f>
+        <f t="shared" si="0"/>
         <v>864</v>
       </c>
       <c r="J57" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>576</v>
       </c>
       <c r="K57" s="16" t="s">
@@ -3360,26 +3358,18 @@
       <c r="E58" s="14"/>
       <c r="F58" s="14"/>
       <c r="G58" s="14"/>
-      <c r="H58" s="14">
-        <v>130</v>
-      </c>
-      <c r="I58" s="15">
-        <f>IF(SUM(B58:F58,H58)=0,"",SUM(B58:F58,H58))</f>
-        <v>130</v>
-      </c>
-      <c r="J58" s="15">
+      <c r="H58" s="14"/>
+      <c r="I58" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1310</v>
-      </c>
-      <c r="K58" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L58" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M58" s="16" t="s">
-        <v>58</v>
-      </c>
+        <v/>
+      </c>
+      <c r="J58" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
@@ -3392,11 +3382,11 @@
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
       <c r="I59" s="15" t="str">
-        <f>IF(SUM(B59:F59,H59)=0,"",SUM(B59:F59,H59))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J59" s="15" t="str">
-        <f t="shared" ref="J59:J109" si="1">IF(I59="","",1440-I59)</f>
+        <f t="shared" ref="J59:J109" si="2">IF(I59="","",1440-I59)</f>
         <v/>
       </c>
       <c r="K59" s="16"/>
@@ -3414,11 +3404,11 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="15" t="str">
-        <f>IF(SUM(B60:F60,H60)=0,"",SUM(B60:F60,H60))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J60" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K60" s="16"/>
@@ -3436,11 +3426,11 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
-        <f>IF(SUM(B61:F61,H61)=0,"",SUM(B61:F61,H61))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J61" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K61" s="16"/>
@@ -3458,11 +3448,11 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
-        <f>IF(SUM(B62:F62,H62)=0,"",SUM(B62:F62,H62))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J62" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K62" s="16"/>
@@ -3480,11 +3470,11 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
-        <f>IF(SUM(B63:F63,H63)=0,"",SUM(B63:F63,H63))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K63" s="16"/>
@@ -3502,11 +3492,11 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
-        <f>IF(SUM(B64:F64,H64)=0,"",SUM(B64:F64,H64))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J64" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K64" s="16"/>
@@ -3524,11 +3514,11 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f>IF(SUM(B65:F65,H65)=0,"",SUM(B65:F65,H65))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K65" s="16"/>
@@ -3546,11 +3536,11 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="15" t="str">
-        <f>IF(SUM(B66:F66,H66)=0,"",SUM(B66:F66,H66))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J66" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K66" s="16"/>
@@ -3568,11 +3558,11 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="15" t="str">
-        <f>IF(SUM(B67:F67,H67)=0,"",SUM(B67:F67,H67))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J67" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K67" s="16"/>
@@ -3590,11 +3580,11 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
-        <f>IF(SUM(B68:F68,H68)=0,"",SUM(B68:F68,H68))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -3612,11 +3602,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f>IF(SUM(B69:F69,H69)=0,"",SUM(B69:F69,H69))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3634,11 +3624,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f>IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="3">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3656,11 +3646,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f>IF(SUM(B71:F71,H71)=0,"",SUM(B71:F71,H71))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3678,11 +3668,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f>IF(SUM(B72:F72,H72)=0,"",SUM(B72:F72,H72))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3700,11 +3690,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f>IF(SUM(B73:F73,H73)=0,"",SUM(B73:F73,H73))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3722,11 +3712,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f>IF(SUM(B74:F74,H74)=0,"",SUM(B74:F74,H74))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3744,11 +3734,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f>IF(SUM(B75:F75,H75)=0,"",SUM(B75:F75,H75))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3766,11 +3756,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f>IF(SUM(B76:F76,H76)=0,"",SUM(B76:F76,H76))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3788,11 +3778,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f>IF(SUM(B77:F77,H77)=0,"",SUM(B77:F77,H77))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3810,11 +3800,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f>IF(SUM(B78:F78,H78)=0,"",SUM(B78:F78,H78))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3832,11 +3822,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f>IF(SUM(B79:F79,H79)=0,"",SUM(B79:F79,H79))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3854,11 +3844,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f>IF(SUM(B80:F80,H80)=0,"",SUM(B80:F80,H80))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3876,11 +3866,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f>IF(SUM(B81:F81,H81)=0,"",SUM(B81:F81,H81))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3898,11 +3888,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f>IF(SUM(B82:F82,H82)=0,"",SUM(B82:F82,H82))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3920,11 +3910,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f>IF(SUM(B83:F83,H83)=0,"",SUM(B83:F83,H83))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3942,11 +3932,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f>IF(SUM(B84:F84,H84)=0,"",SUM(B84:F84,H84))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3964,11 +3954,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f>IF(SUM(B85:F85,H85)=0,"",SUM(B85:F85,H85))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3986,11 +3976,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f>IF(SUM(B86:F86,H86)=0,"",SUM(B86:F86,H86))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -4008,11 +3998,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f>IF(SUM(B87:F87,H87)=0,"",SUM(B87:F87,H87))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -4030,11 +4020,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f>IF(SUM(B88:F88,H88)=0,"",SUM(B88:F88,H88))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -4052,11 +4042,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f>IF(SUM(B89:F89,H89)=0,"",SUM(B89:F89,H89))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -4074,11 +4064,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f>IF(SUM(B90:F90,H90)=0,"",SUM(B90:F90,H90))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -4096,11 +4086,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f>IF(SUM(B91:F91,H91)=0,"",SUM(B91:F91,H91))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -4118,11 +4108,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f>IF(SUM(B92:F92,H92)=0,"",SUM(B92:F92,H92))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -4140,11 +4130,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f>IF(SUM(B93:F93,H93)=0,"",SUM(B93:F93,H93))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -4162,11 +4152,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f>IF(SUM(B94:F94,H94)=0,"",SUM(B94:F94,H94))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -4184,11 +4174,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f>IF(SUM(B95:F95,H95)=0,"",SUM(B95:F95,H95))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -4206,11 +4196,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f>IF(SUM(B96:F96,H96)=0,"",SUM(B96:F96,H96))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -4228,11 +4218,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f>IF(SUM(B97:F97,H97)=0,"",SUM(B97:F97,H97))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -4250,11 +4240,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f>IF(SUM(B98:F98,H98)=0,"",SUM(B98:F98,H98))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -4272,11 +4262,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f>IF(SUM(B99:F99,H99)=0,"",SUM(B99:F99,H99))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -4294,11 +4284,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f>IF(SUM(B100:F100,H100)=0,"",SUM(B100:F100,H100))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -4316,11 +4306,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f>IF(SUM(B101:F101,H101)=0,"",SUM(B101:F101,H101))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -4338,11 +4328,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f>IF(SUM(B102:F102,H102)=0,"",SUM(B102:F102,H102))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -4360,11 +4350,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f>IF(SUM(B103:F103,H103)=0,"",SUM(B103:F103,H103))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -4382,11 +4372,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f>IF(SUM(B104:F104,H104)=0,"",SUM(B104:F104,H104))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -4404,11 +4394,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f>IF(SUM(B105:F105,H105)=0,"",SUM(B105:F105,H105))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -4426,11 +4416,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f>IF(SUM(B106:F106,H106)=0,"",SUM(B106:F106,H106))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -4448,11 +4438,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f>IF(SUM(B107:F107,H107)=0,"",SUM(B107:F107,H107))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -4470,11 +4460,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f>IF(SUM(B108:F108,H108)=0,"",SUM(B108:F108,H108))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -4492,11 +4482,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f>IF(SUM(B109:F109,H109)=0,"",SUM(B109:F109,H109))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -4514,11 +4504,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f>IF(SUM(B110:F110,H110)=0,"",SUM(B110:F110,H110))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" ref="J110:J173" si="2">IF(I110="","",1440-I110)</f>
+        <f t="shared" ref="J110:J173" si="4">IF(I110="","",1440-I110)</f>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -4536,11 +4526,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f>IF(SUM(B111:F111,H111)=0,"",SUM(B111:F111,H111))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -4558,11 +4548,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f>IF(SUM(B112:F112,H112)=0,"",SUM(B112:F112,H112))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -4580,11 +4570,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f>IF(SUM(B113:F113,H113)=0,"",SUM(B113:F113,H113))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -4602,11 +4592,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f>IF(SUM(B114:F114,H114)=0,"",SUM(B114:F114,H114))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -4624,11 +4614,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f>IF(SUM(B115:F115,H115)=0,"",SUM(B115:F115,H115))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4646,11 +4636,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f>IF(SUM(B116:F116,H116)=0,"",SUM(B116:F116,H116))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4668,11 +4658,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f>IF(SUM(B117:F117,H117)=0,"",SUM(B117:F117,H117))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4690,11 +4680,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f>IF(SUM(B118:F118,H118)=0,"",SUM(B118:F118,H118))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4712,11 +4702,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f>IF(SUM(B119:F119,H119)=0,"",SUM(B119:F119,H119))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4734,11 +4724,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f>IF(SUM(B120:F120,H120)=0,"",SUM(B120:F120,H120))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4756,11 +4746,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f>IF(SUM(B121:F121,H121)=0,"",SUM(B121:F121,H121))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4778,11 +4768,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f>IF(SUM(B122:F122,H122)=0,"",SUM(B122:F122,H122))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4800,11 +4790,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f>IF(SUM(B123:F123,H123)=0,"",SUM(B123:F123,H123))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4822,11 +4812,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f>IF(SUM(B124:F124,H124)=0,"",SUM(B124:F124,H124))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4844,11 +4834,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f>IF(SUM(B125:F125,H125)=0,"",SUM(B125:F125,H125))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4866,11 +4856,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f>IF(SUM(B126:F126,H126)=0,"",SUM(B126:F126,H126))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4888,11 +4878,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f>IF(SUM(B127:F127,H127)=0,"",SUM(B127:F127,H127))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4910,11 +4900,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f>IF(SUM(B128:F128,H128)=0,"",SUM(B128:F128,H128))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4932,11 +4922,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f>IF(SUM(B129:F129,H129)=0,"",SUM(B129:F129,H129))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4954,11 +4944,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f>IF(SUM(B130:F130,H130)=0,"",SUM(B130:F130,H130))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4976,11 +4966,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f>IF(SUM(B131:F131,H131)=0,"",SUM(B131:F131,H131))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4998,11 +4988,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f>IF(SUM(B132:F132,H132)=0,"",SUM(B132:F132,H132))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -5020,11 +5010,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f>IF(SUM(B133:F133,H133)=0,"",SUM(B133:F133,H133))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -5042,11 +5032,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f>IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="5">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -5064,11 +5054,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f>IF(SUM(B135:F135,H135)=0,"",SUM(B135:F135,H135))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -5086,11 +5076,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f>IF(SUM(B136:F136,H136)=0,"",SUM(B136:F136,H136))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -5108,11 +5098,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f>IF(SUM(B137:F137,H137)=0,"",SUM(B137:F137,H137))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -5130,11 +5120,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f>IF(SUM(B138:F138,H138)=0,"",SUM(B138:F138,H138))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -5152,11 +5142,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f>IF(SUM(B139:F139,H139)=0,"",SUM(B139:F139,H139))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -5174,11 +5164,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f>IF(SUM(B140:F140,H140)=0,"",SUM(B140:F140,H140))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -5196,11 +5186,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f>IF(SUM(B141:F141,H141)=0,"",SUM(B141:F141,H141))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -5218,11 +5208,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f>IF(SUM(B142:F142,H142)=0,"",SUM(B142:F142,H142))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -5240,11 +5230,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f>IF(SUM(B143:F143,H143)=0,"",SUM(B143:F143,H143))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -5262,11 +5252,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f>IF(SUM(B144:F144,H144)=0,"",SUM(B144:F144,H144))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -5284,11 +5274,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f>IF(SUM(B145:F145,H145)=0,"",SUM(B145:F145,H145))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -5306,11 +5296,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f>IF(SUM(B146:F146,H146)=0,"",SUM(B146:F146,H146))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -5328,11 +5318,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f>IF(SUM(B147:F147,H147)=0,"",SUM(B147:F147,H147))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -5350,11 +5340,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f>IF(SUM(B148:F148,H148)=0,"",SUM(B148:F148,H148))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -5372,11 +5362,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f>IF(SUM(B149:F149,H149)=0,"",SUM(B149:F149,H149))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -5394,11 +5384,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f>IF(SUM(B150:F150,H150)=0,"",SUM(B150:F150,H150))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -5416,11 +5406,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f>IF(SUM(B151:F151,H151)=0,"",SUM(B151:F151,H151))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -5438,11 +5428,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f>IF(SUM(B152:F152,H152)=0,"",SUM(B152:F152,H152))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -5460,11 +5450,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f>IF(SUM(B153:F153,H153)=0,"",SUM(B153:F153,H153))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -5482,11 +5472,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f>IF(SUM(B154:F154,H154)=0,"",SUM(B154:F154,H154))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -5504,11 +5494,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f>IF(SUM(B155:F155,H155)=0,"",SUM(B155:F155,H155))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -5526,11 +5516,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f>IF(SUM(B156:F156,H156)=0,"",SUM(B156:F156,H156))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -5548,11 +5538,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f>IF(SUM(B157:F157,H157)=0,"",SUM(B157:F157,H157))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -5570,11 +5560,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f>IF(SUM(B158:F158,H158)=0,"",SUM(B158:F158,H158))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -5592,11 +5582,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f>IF(SUM(B159:F159,H159)=0,"",SUM(B159:F159,H159))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -5614,11 +5604,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f>IF(SUM(B160:F160,H160)=0,"",SUM(B160:F160,H160))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5636,11 +5626,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f>IF(SUM(B161:F161,H161)=0,"",SUM(B161:F161,H161))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5658,11 +5648,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f>IF(SUM(B162:F162,H162)=0,"",SUM(B162:F162,H162))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5680,11 +5670,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f>IF(SUM(B163:F163,H163)=0,"",SUM(B163:F163,H163))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5702,11 +5692,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f>IF(SUM(B164:F164,H164)=0,"",SUM(B164:F164,H164))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5724,11 +5714,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f>IF(SUM(B165:F165,H165)=0,"",SUM(B165:F165,H165))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5746,11 +5736,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f>IF(SUM(B166:F166,H166)=0,"",SUM(B166:F166,H166))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5768,11 +5758,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f>IF(SUM(B167:F167,H167)=0,"",SUM(B167:F167,H167))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5790,11 +5780,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f>IF(SUM(B168:F168,H168)=0,"",SUM(B168:F168,H168))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5812,11 +5802,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f>IF(SUM(B169:F169,H169)=0,"",SUM(B169:F169,H169))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5834,11 +5824,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f>IF(SUM(B170:F170,H170)=0,"",SUM(B170:F170,H170))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5856,11 +5846,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f>IF(SUM(B171:F171,H171)=0,"",SUM(B171:F171,H171))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5878,11 +5868,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f>IF(SUM(B172:F172,H172)=0,"",SUM(B172:F172,H172))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5900,11 +5890,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f>IF(SUM(B173:F173,H173)=0,"",SUM(B173:F173,H173))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5922,11 +5912,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f>IF(SUM(B174:F174,H174)=0,"",SUM(B174:F174,H174))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" ref="J174:J237" si="3">IF(I174="","",1440-I174)</f>
+        <f t="shared" ref="J174:J237" si="6">IF(I174="","",1440-I174)</f>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5944,11 +5934,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f>IF(SUM(B175:F175,H175)=0,"",SUM(B175:F175,H175))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5966,11 +5956,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f>IF(SUM(B176:F176,H176)=0,"",SUM(B176:F176,H176))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5988,11 +5978,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f>IF(SUM(B177:F177,H177)=0,"",SUM(B177:F177,H177))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -6010,11 +6000,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f>IF(SUM(B178:F178,H178)=0,"",SUM(B178:F178,H178))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -6032,11 +6022,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f>IF(SUM(B179:F179,H179)=0,"",SUM(B179:F179,H179))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -6054,11 +6044,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f>IF(SUM(B180:F180,H180)=0,"",SUM(B180:F180,H180))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -6076,11 +6066,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f>IF(SUM(B181:F181,H181)=0,"",SUM(B181:F181,H181))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -6098,11 +6088,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f>IF(SUM(B182:F182,H182)=0,"",SUM(B182:F182,H182))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -6120,11 +6110,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f>IF(SUM(B183:F183,H183)=0,"",SUM(B183:F183,H183))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -6142,11 +6132,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f>IF(SUM(B184:F184,H184)=0,"",SUM(B184:F184,H184))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -6164,11 +6154,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f>IF(SUM(B185:F185,H185)=0,"",SUM(B185:F185,H185))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -6186,11 +6176,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f>IF(SUM(B186:F186,H186)=0,"",SUM(B186:F186,H186))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -6208,11 +6198,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f>IF(SUM(B187:F187,H187)=0,"",SUM(B187:F187,H187))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -6230,11 +6220,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f>IF(SUM(B188:F188,H188)=0,"",SUM(B188:F188,H188))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -6252,11 +6242,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f>IF(SUM(B189:F189,H189)=0,"",SUM(B189:F189,H189))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -6274,11 +6264,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f>IF(SUM(B190:F190,H190)=0,"",SUM(B190:F190,H190))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -6296,11 +6286,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f>IF(SUM(B191:F191,H191)=0,"",SUM(B191:F191,H191))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -6318,11 +6308,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f>IF(SUM(B192:F192,H192)=0,"",SUM(B192:F192,H192))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -6340,11 +6330,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f>IF(SUM(B193:F193,H193)=0,"",SUM(B193:F193,H193))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6362,11 +6352,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f>IF(SUM(B194:F194,H194)=0,"",SUM(B194:F194,H194))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -6384,11 +6374,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f>IF(SUM(B195:F195,H195)=0,"",SUM(B195:F195,H195))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -6406,11 +6396,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f>IF(SUM(B196:F196,H196)=0,"",SUM(B196:F196,H196))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -6428,11 +6418,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f>IF(SUM(B197:F197,H197)=0,"",SUM(B197:F197,H197))</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -6450,11 +6440,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f>IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="7">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6472,11 +6462,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f>IF(SUM(B199:F199,H199)=0,"",SUM(B199:F199,H199))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6494,11 +6484,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f>IF(SUM(B200:F200,H200)=0,"",SUM(B200:F200,H200))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6516,11 +6506,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f>IF(SUM(B201:F201,H201)=0,"",SUM(B201:F201,H201))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6538,11 +6528,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f>IF(SUM(B202:F202,H202)=0,"",SUM(B202:F202,H202))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -6560,11 +6550,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f>IF(SUM(B203:F203,H203)=0,"",SUM(B203:F203,H203))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -6582,11 +6572,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f>IF(SUM(B204:F204,H204)=0,"",SUM(B204:F204,H204))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -6604,11 +6594,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f>IF(SUM(B205:F205,H205)=0,"",SUM(B205:F205,H205))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6626,11 +6616,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f>IF(SUM(B206:F206,H206)=0,"",SUM(B206:F206,H206))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6648,11 +6638,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f>IF(SUM(B207:F207,H207)=0,"",SUM(B207:F207,H207))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6670,11 +6660,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f>IF(SUM(B208:F208,H208)=0,"",SUM(B208:F208,H208))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6692,11 +6682,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f>IF(SUM(B209:F209,H209)=0,"",SUM(B209:F209,H209))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6714,11 +6704,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f>IF(SUM(B210:F210,H210)=0,"",SUM(B210:F210,H210))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6736,11 +6726,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f>IF(SUM(B211:F211,H211)=0,"",SUM(B211:F211,H211))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6758,11 +6748,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f>IF(SUM(B212:F212,H212)=0,"",SUM(B212:F212,H212))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6780,11 +6770,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f>IF(SUM(B213:F213,H213)=0,"",SUM(B213:F213,H213))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6802,11 +6792,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f>IF(SUM(B214:F214,H214)=0,"",SUM(B214:F214,H214))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6824,11 +6814,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f>IF(SUM(B215:F215,H215)=0,"",SUM(B215:F215,H215))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6846,11 +6836,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f>IF(SUM(B216:F216,H216)=0,"",SUM(B216:F216,H216))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6868,11 +6858,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f>IF(SUM(B217:F217,H217)=0,"",SUM(B217:F217,H217))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6890,11 +6880,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f>IF(SUM(B218:F218,H218)=0,"",SUM(B218:F218,H218))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6912,11 +6902,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f>IF(SUM(B219:F219,H219)=0,"",SUM(B219:F219,H219))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6934,11 +6924,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f>IF(SUM(B220:F220,H220)=0,"",SUM(B220:F220,H220))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6956,11 +6946,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f>IF(SUM(B221:F221,H221)=0,"",SUM(B221:F221,H221))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6978,11 +6968,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f>IF(SUM(B222:F222,H222)=0,"",SUM(B222:F222,H222))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -7000,11 +6990,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f>IF(SUM(B223:F223,H223)=0,"",SUM(B223:F223,H223))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -7022,11 +7012,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f>IF(SUM(B224:F224,H224)=0,"",SUM(B224:F224,H224))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -7044,11 +7034,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f>IF(SUM(B225:F225,H225)=0,"",SUM(B225:F225,H225))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -7066,11 +7056,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f>IF(SUM(B226:F226,H226)=0,"",SUM(B226:F226,H226))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -7088,11 +7078,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f>IF(SUM(B227:F227,H227)=0,"",SUM(B227:F227,H227))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -7110,11 +7100,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f>IF(SUM(B228:F228,H228)=0,"",SUM(B228:F228,H228))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -7132,11 +7122,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f>IF(SUM(B229:F229,H229)=0,"",SUM(B229:F229,H229))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -7154,11 +7144,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f>IF(SUM(B230:F230,H230)=0,"",SUM(B230:F230,H230))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -7176,11 +7166,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f>IF(SUM(B231:F231,H231)=0,"",SUM(B231:F231,H231))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -7198,11 +7188,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f>IF(SUM(B232:F232,H232)=0,"",SUM(B232:F232,H232))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -7220,11 +7210,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f>IF(SUM(B233:F233,H233)=0,"",SUM(B233:F233,H233))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -7242,11 +7232,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f>IF(SUM(B234:F234,H234)=0,"",SUM(B234:F234,H234))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -7264,11 +7254,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f>IF(SUM(B235:F235,H235)=0,"",SUM(B235:F235,H235))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -7286,11 +7276,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f>IF(SUM(B236:F236,H236)=0,"",SUM(B236:F236,H236))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -7308,11 +7298,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f>IF(SUM(B237:F237,H237)=0,"",SUM(B237:F237,H237))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -7330,11 +7320,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f>IF(SUM(B238:F238,H238)=0,"",SUM(B238:F238,H238))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" ref="J238:J301" si="4">IF(I238="","",1440-I238)</f>
+        <f t="shared" ref="J238:J301" si="8">IF(I238="","",1440-I238)</f>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -7352,11 +7342,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f>IF(SUM(B239:F239,H239)=0,"",SUM(B239:F239,H239))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -7374,11 +7364,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f>IF(SUM(B240:F240,H240)=0,"",SUM(B240:F240,H240))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -7396,11 +7386,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f>IF(SUM(B241:F241,H241)=0,"",SUM(B241:F241,H241))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -7418,11 +7408,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f>IF(SUM(B242:F242,H242)=0,"",SUM(B242:F242,H242))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -7440,11 +7430,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f>IF(SUM(B243:F243,H243)=0,"",SUM(B243:F243,H243))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -7462,11 +7452,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f>IF(SUM(B244:F244,H244)=0,"",SUM(B244:F244,H244))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -7484,11 +7474,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f>IF(SUM(B245:F245,H245)=0,"",SUM(B245:F245,H245))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -7506,11 +7496,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f>IF(SUM(B246:F246,H246)=0,"",SUM(B246:F246,H246))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -7528,11 +7518,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f>IF(SUM(B247:F247,H247)=0,"",SUM(B247:F247,H247))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -7550,11 +7540,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f>IF(SUM(B248:F248,H248)=0,"",SUM(B248:F248,H248))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -7572,11 +7562,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f>IF(SUM(B249:F249,H249)=0,"",SUM(B249:F249,H249))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -7594,11 +7584,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f>IF(SUM(B250:F250,H250)=0,"",SUM(B250:F250,H250))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -7616,11 +7606,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f>IF(SUM(B251:F251,H251)=0,"",SUM(B251:F251,H251))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7638,11 +7628,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f>IF(SUM(B252:F252,H252)=0,"",SUM(B252:F252,H252))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7660,11 +7650,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f>IF(SUM(B253:F253,H253)=0,"",SUM(B253:F253,H253))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7682,11 +7672,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f>IF(SUM(B254:F254,H254)=0,"",SUM(B254:F254,H254))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7704,11 +7694,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f>IF(SUM(B255:F255,H255)=0,"",SUM(B255:F255,H255))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7726,11 +7716,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f>IF(SUM(B256:F256,H256)=0,"",SUM(B256:F256,H256))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7748,11 +7738,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f>IF(SUM(B257:F257,H257)=0,"",SUM(B257:F257,H257))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7770,11 +7760,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f>IF(SUM(B258:F258,H258)=0,"",SUM(B258:F258,H258))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7792,11 +7782,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f>IF(SUM(B259:F259,H259)=0,"",SUM(B259:F259,H259))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7814,11 +7804,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f>IF(SUM(B260:F260,H260)=0,"",SUM(B260:F260,H260))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7836,11 +7826,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f>IF(SUM(B261:F261,H261)=0,"",SUM(B261:F261,H261))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7858,11 +7848,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f>IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="9">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7880,11 +7870,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f>IF(SUM(B263:F263,H263)=0,"",SUM(B263:F263,H263))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7902,11 +7892,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f>IF(SUM(B264:F264,H264)=0,"",SUM(B264:F264,H264))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7924,11 +7914,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f>IF(SUM(B265:F265,H265)=0,"",SUM(B265:F265,H265))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7946,11 +7936,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f>IF(SUM(B266:F266,H266)=0,"",SUM(B266:F266,H266))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7968,11 +7958,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f>IF(SUM(B267:F267,H267)=0,"",SUM(B267:F267,H267))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7990,11 +7980,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f>IF(SUM(B268:F268,H268)=0,"",SUM(B268:F268,H268))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -8012,11 +8002,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f>IF(SUM(B269:F269,H269)=0,"",SUM(B269:F269,H269))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -8034,11 +8024,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f>IF(SUM(B270:F270,H270)=0,"",SUM(B270:F270,H270))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -8056,11 +8046,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f>IF(SUM(B271:F271,H271)=0,"",SUM(B271:F271,H271))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -8078,11 +8068,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f>IF(SUM(B272:F272,H272)=0,"",SUM(B272:F272,H272))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -8100,11 +8090,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f>IF(SUM(B273:F273,H273)=0,"",SUM(B273:F273,H273))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -8122,11 +8112,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f>IF(SUM(B274:F274,H274)=0,"",SUM(B274:F274,H274))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -8144,11 +8134,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f>IF(SUM(B275:F275,H275)=0,"",SUM(B275:F275,H275))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -8166,11 +8156,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f>IF(SUM(B276:F276,H276)=0,"",SUM(B276:F276,H276))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -8188,11 +8178,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f>IF(SUM(B277:F277,H277)=0,"",SUM(B277:F277,H277))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -8210,11 +8200,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f>IF(SUM(B278:F278,H278)=0,"",SUM(B278:F278,H278))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -8232,11 +8222,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f>IF(SUM(B279:F279,H279)=0,"",SUM(B279:F279,H279))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -8254,11 +8244,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f>IF(SUM(B280:F280,H280)=0,"",SUM(B280:F280,H280))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -8276,11 +8266,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f>IF(SUM(B281:F281,H281)=0,"",SUM(B281:F281,H281))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -8298,11 +8288,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f>IF(SUM(B282:F282,H282)=0,"",SUM(B282:F282,H282))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -8320,11 +8310,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f>IF(SUM(B283:F283,H283)=0,"",SUM(B283:F283,H283))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -8342,11 +8332,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f>IF(SUM(B284:F284,H284)=0,"",SUM(B284:F284,H284))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -8364,11 +8354,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f>IF(SUM(B285:F285,H285)=0,"",SUM(B285:F285,H285))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -8386,11 +8376,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f>IF(SUM(B286:F286,H286)=0,"",SUM(B286:F286,H286))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -8408,11 +8398,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f>IF(SUM(B287:F287,H287)=0,"",SUM(B287:F287,H287))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -8430,11 +8420,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f>IF(SUM(B288:F288,H288)=0,"",SUM(B288:F288,H288))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -8452,11 +8442,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f>IF(SUM(B289:F289,H289)=0,"",SUM(B289:F289,H289))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -8474,11 +8464,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f>IF(SUM(B290:F290,H290)=0,"",SUM(B290:F290,H290))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -8496,11 +8486,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f>IF(SUM(B291:F291,H291)=0,"",SUM(B291:F291,H291))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -8518,11 +8508,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f>IF(SUM(B292:F292,H292)=0,"",SUM(B292:F292,H292))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -8540,11 +8530,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f>IF(SUM(B293:F293,H293)=0,"",SUM(B293:F293,H293))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -8562,11 +8552,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f>IF(SUM(B294:F294,H294)=0,"",SUM(B294:F294,H294))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -8584,11 +8574,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f>IF(SUM(B295:F295,H295)=0,"",SUM(B295:F295,H295))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -8606,11 +8596,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f>IF(SUM(B296:F296,H296)=0,"",SUM(B296:F296,H296))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8628,11 +8618,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f>IF(SUM(B297:F297,H297)=0,"",SUM(B297:F297,H297))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8650,11 +8640,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f>IF(SUM(B298:F298,H298)=0,"",SUM(B298:F298,H298))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8672,11 +8662,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f>IF(SUM(B299:F299,H299)=0,"",SUM(B299:F299,H299))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8694,11 +8684,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f>IF(SUM(B300:F300,H300)=0,"",SUM(B300:F300,H300))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8716,11 +8706,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f>IF(SUM(B301:F301,H301)=0,"",SUM(B301:F301,H301))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8738,11 +8728,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f>IF(SUM(B302:F302,H302)=0,"",SUM(B302:F302,H302))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" ref="J302:J365" si="5">IF(I302="","",1440-I302)</f>
+        <f t="shared" ref="J302:J365" si="10">IF(I302="","",1440-I302)</f>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8760,11 +8750,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f>IF(SUM(B303:F303,H303)=0,"",SUM(B303:F303,H303))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8782,11 +8772,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f>IF(SUM(B304:F304,H304)=0,"",SUM(B304:F304,H304))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8804,11 +8794,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f>IF(SUM(B305:F305,H305)=0,"",SUM(B305:F305,H305))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8826,11 +8816,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f>IF(SUM(B306:F306,H306)=0,"",SUM(B306:F306,H306))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8848,11 +8838,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f>IF(SUM(B307:F307,H307)=0,"",SUM(B307:F307,H307))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8870,11 +8860,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f>IF(SUM(B308:F308,H308)=0,"",SUM(B308:F308,H308))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8892,11 +8882,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f>IF(SUM(B309:F309,H309)=0,"",SUM(B309:F309,H309))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8914,11 +8904,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f>IF(SUM(B310:F310,H310)=0,"",SUM(B310:F310,H310))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8936,11 +8926,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f>IF(SUM(B311:F311,H311)=0,"",SUM(B311:F311,H311))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8958,11 +8948,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f>IF(SUM(B312:F312,H312)=0,"",SUM(B312:F312,H312))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8980,11 +8970,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f>IF(SUM(B313:F313,H313)=0,"",SUM(B313:F313,H313))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -9002,11 +8992,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f>IF(SUM(B314:F314,H314)=0,"",SUM(B314:F314,H314))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -9024,11 +9014,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f>IF(SUM(B315:F315,H315)=0,"",SUM(B315:F315,H315))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -9046,11 +9036,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f>IF(SUM(B316:F316,H316)=0,"",SUM(B316:F316,H316))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -9068,11 +9058,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f>IF(SUM(B317:F317,H317)=0,"",SUM(B317:F317,H317))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -9090,11 +9080,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f>IF(SUM(B318:F318,H318)=0,"",SUM(B318:F318,H318))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -9112,11 +9102,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f>IF(SUM(B319:F319,H319)=0,"",SUM(B319:F319,H319))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -9134,11 +9124,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f>IF(SUM(B320:F320,H320)=0,"",SUM(B320:F320,H320))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -9156,11 +9146,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f>IF(SUM(B321:F321,H321)=0,"",SUM(B321:F321,H321))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9178,11 +9168,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f>IF(SUM(B322:F322,H322)=0,"",SUM(B322:F322,H322))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -9200,11 +9190,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f>IF(SUM(B323:F323,H323)=0,"",SUM(B323:F323,H323))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -9222,11 +9212,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f>IF(SUM(B324:F324,H324)=0,"",SUM(B324:F324,H324))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -9244,11 +9234,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f>IF(SUM(B325:F325,H325)=0,"",SUM(B325:F325,H325))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -9266,11 +9256,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f>IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="11">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9288,11 +9278,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f>IF(SUM(B327:F327,H327)=0,"",SUM(B327:F327,H327))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9310,11 +9300,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f>IF(SUM(B328:F328,H328)=0,"",SUM(B328:F328,H328))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9332,11 +9322,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f>IF(SUM(B329:F329,H329)=0,"",SUM(B329:F329,H329))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9354,11 +9344,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f>IF(SUM(B330:F330,H330)=0,"",SUM(B330:F330,H330))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -9376,11 +9366,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f>IF(SUM(B331:F331,H331)=0,"",SUM(B331:F331,H331))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -9398,11 +9388,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f>IF(SUM(B332:F332,H332)=0,"",SUM(B332:F332,H332))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -9420,11 +9410,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f>IF(SUM(B333:F333,H333)=0,"",SUM(B333:F333,H333))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -9442,11 +9432,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f>IF(SUM(B334:F334,H334)=0,"",SUM(B334:F334,H334))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -9464,11 +9454,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f>IF(SUM(B335:F335,H335)=0,"",SUM(B335:F335,H335))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -9486,11 +9476,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f>IF(SUM(B336:F336,H336)=0,"",SUM(B336:F336,H336))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -9508,11 +9498,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f>IF(SUM(B337:F337,H337)=0,"",SUM(B337:F337,H337))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -9530,11 +9520,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f>IF(SUM(B338:F338,H338)=0,"",SUM(B338:F338,H338))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -9552,11 +9542,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f>IF(SUM(B339:F339,H339)=0,"",SUM(B339:F339,H339))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -9574,11 +9564,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f>IF(SUM(B340:F340,H340)=0,"",SUM(B340:F340,H340))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -9596,11 +9586,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f>IF(SUM(B341:F341,H341)=0,"",SUM(B341:F341,H341))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -9618,11 +9608,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f>IF(SUM(B342:F342,H342)=0,"",SUM(B342:F342,H342))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -9640,11 +9630,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f>IF(SUM(B343:F343,H343)=0,"",SUM(B343:F343,H343))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -9662,11 +9652,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f>IF(SUM(B344:F344,H344)=0,"",SUM(B344:F344,H344))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -9684,11 +9674,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f>IF(SUM(B345:F345,H345)=0,"",SUM(B345:F345,H345))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -9706,11 +9696,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f>IF(SUM(B346:F346,H346)=0,"",SUM(B346:F346,H346))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -9728,11 +9718,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f>IF(SUM(B347:F347,H347)=0,"",SUM(B347:F347,H347))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -9750,11 +9740,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f>IF(SUM(B348:F348,H348)=0,"",SUM(B348:F348,H348))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -9772,11 +9762,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f>IF(SUM(B349:F349,H349)=0,"",SUM(B349:F349,H349))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -9794,11 +9784,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f>IF(SUM(B350:F350,H350)=0,"",SUM(B350:F350,H350))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -9816,11 +9806,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f>IF(SUM(B351:F351,H351)=0,"",SUM(B351:F351,H351))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -9838,11 +9828,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f>IF(SUM(B352:F352,H352)=0,"",SUM(B352:F352,H352))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -9860,11 +9850,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f>IF(SUM(B353:F353,H353)=0,"",SUM(B353:F353,H353))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -9882,11 +9872,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f>IF(SUM(B354:F354,H354)=0,"",SUM(B354:F354,H354))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -9904,11 +9894,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f>IF(SUM(B355:F355,H355)=0,"",SUM(B355:F355,H355))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9926,11 +9916,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f>IF(SUM(B356:F356,H356)=0,"",SUM(B356:F356,H356))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9948,11 +9938,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f>IF(SUM(B357:F357,H357)=0,"",SUM(B357:F357,H357))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9970,11 +9960,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f>IF(SUM(B358:F358,H358)=0,"",SUM(B358:F358,H358))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9992,11 +9982,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f>IF(SUM(B359:F359,H359)=0,"",SUM(B359:F359,H359))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -10014,11 +10004,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f>IF(SUM(B360:F360,H360)=0,"",SUM(B360:F360,H360))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -10036,11 +10026,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f>IF(SUM(B361:F361,H361)=0,"",SUM(B361:F361,H361))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -10058,11 +10048,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f>IF(SUM(B362:F362,H362)=0,"",SUM(B362:F362,H362))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -10080,11 +10070,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f>IF(SUM(B363:F363,H363)=0,"",SUM(B363:F363,H363))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -10102,11 +10092,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f>IF(SUM(B364:F364,H364)=0,"",SUM(B364:F364,H364))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -10124,11 +10114,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f>IF(SUM(B365:F365,H365)=0,"",SUM(B365:F365,H365))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -10146,11 +10136,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f>IF(SUM(B366:F366,H366)=0,"",SUM(B366:F366,H366))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" ref="J366:J377" si="6">IF(I366="","",1440-I366)</f>
+        <f t="shared" ref="J366:J377" si="12">IF(I366="","",1440-I366)</f>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -10168,11 +10158,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f>IF(SUM(B367:F367,H367)=0,"",SUM(B367:F367,H367))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -10190,11 +10180,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f>IF(SUM(B368:F368,H368)=0,"",SUM(B368:F368,H368))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -10212,11 +10202,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f>IF(SUM(B369:F369,H369)=0,"",SUM(B369:F369,H369))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -10234,11 +10224,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f>IF(SUM(B370:F370,H370)=0,"",SUM(B370:F370,H370))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -10256,11 +10246,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f>IF(SUM(B371:F371,H371)=0,"",SUM(B371:F371,H371))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -10278,11 +10268,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f>IF(SUM(B372:F372,H372)=0,"",SUM(B372:F372,H372))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -10300,11 +10290,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f>IF(SUM(B373:F373,H373)=0,"",SUM(B373:F373,H373))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -10322,11 +10312,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f>IF(SUM(B374:F374,H374)=0,"",SUM(B374:F374,H374))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -10344,11 +10334,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f>IF(SUM(B375:F375,H375)=0,"",SUM(B375:F375,H375))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -10366,11 +10356,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f>IF(SUM(B376:F376,H376)=0,"",SUM(B376:F376,H376))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -10388,11 +10378,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f>IF(SUM(B377:F377,H377)=0,"",SUM(B377:F377,H377))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
